--- a/MonteCarloApp/simulaciones/resultados/CUDA_metricas.xlsx
+++ b/MonteCarloApp/simulaciones/resultados/CUDA_metricas.xlsx
@@ -457,13 +457,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.2586965560913086</v>
+        <v>0.178520679473877</v>
       </c>
       <c r="C2" t="n">
-        <v>156.2421875</v>
+        <v>154.203125</v>
       </c>
       <c r="D2" t="n">
-        <v>8.6</v>
+        <v>9.5</v>
       </c>
     </row>
   </sheetData>

--- a/MonteCarloApp/simulaciones/resultados/CUDA_metricas.xlsx
+++ b/MonteCarloApp/simulaciones/resultados/CUDA_metricas.xlsx
@@ -457,13 +457,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.178520679473877</v>
+        <v>0.137131929397583</v>
       </c>
       <c r="C2" t="n">
-        <v>154.203125</v>
+        <v>151.73046875</v>
       </c>
       <c r="D2" t="n">
-        <v>9.5</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
